--- a/docs/qms/evidence-2026/18_Review_Actions/EM26-18_Review_Feedback_Action_Log.xlsx
+++ b/docs/qms/evidence-2026/18_Review_Actions/EM26-18_Review_Feedback_Action_Log.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Review actions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review actions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/docs/qms/evidence-2026/18_Review_Actions/EM26-18_Review_Feedback_Action_Log.xlsx
+++ b/docs/qms/evidence-2026/18_Review_Actions/EM26-18_Review_Feedback_Action_Log.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review actions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Project history" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review log" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action log" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -428,184 +430,2756 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>When</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Event / requirement / feedback</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Findings</t>
+          <t>Review / action</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Actions</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Effectiveness</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>Evidence</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>RF-2026-001</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Adversarial review: voice speculative reply, tool routing, GPU STT</t>
+          <t>EchoMind (predecessor) delivered a live transcript and a chatbot with RAG on a PC we built for the client, as the client required</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2025 client project</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>All 22 addressed before release. Examples: abort blocking the event loop (socket shutdown before close); WebSocket close not aborting in-flight generation; first-phrase hold released only on a token gap; hold phrase racing the answer; a mid-word text-splitting defect</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>12/12 spoken turns across two personas; barge-in verified; char-offset integrity 0 bad; Silent Assistant unaffected; 0 CUDA errors across ~15 sessions</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Commit ff29843; workflow journal subagents/workflows/wf_cc7bac0b-db9/</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Closed, effectiveness verified</t>
+          <t>2025 evidence pack; EM26-00 §0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>RF-2026-002</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Evaluation-harness review of the paper experiment campaign</t>
+          <t>Portable AI supercomputers (NVIDIA DGX Spark) reach the market; the team decides to move the product to one</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>Management / engineering decision</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>4 substantive, including two that contradict the organisation's own published claims</t>
+          <t>CR-2026-01</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Findings recorded verbatim in eval/paper/results/SUMMARY.json. Paper claims to be corrected in any future version</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Not applicable until a future publication</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>eval/paper/results/SUMMARY.json</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Open — action pending (also REG-04 NC-2026-007)</t>
+          <t>This log</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>RF-2026-003</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Golden-evaluation review of retrieval quality</t>
+          <t>First DGX Spark bought; the 2025 code ported in full and running on it</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-29 → 2026-08-07</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Five retrieval defects in one review (ebd232f), plus a later tenant-isolation regression detected as 50/52 → 42/52</t>
+          <t>AC-20</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Five fixes; then a namespace-enforcing wrapper and corpus-scaled candidate pool (4e27109)</t>
+          <t>4b90b36, c751d79 (2026-02-05)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Requirements from Client A and Client B (Bahrain): (1) personal AI assistant, (2) conversation assistance, (3) financial knowledge base on the DoD Financial Management Regulation (DoD 7000.14-R)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Clients A and B</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-02</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>95d3512 (2026-03-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Conversation assistance v1 on the Kyutai Unmute stack — client: not natural and slow</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Clients A and B</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-03</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>4b90b36 (Moshi adapter), bff6cf2 (Kyutai STT)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>DoD FMR is a very large document: BookRAG and PageIndex tried; hierarchical (section → chunk) chunking adopted for performance</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>AC-22</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>31f1205 … 5057a30 (2026-03-03 → 06); 23ac2f9 (03-07); 2decb99 (07-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03 → 04</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Conversation assistance v2 on NVIDIA PersonaPlex — client: must work with the customer's large data in spoken conversation</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Clients A and B</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-04</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>QASC 2026 paper (539493f)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Own dual-loop conversation architecture built and pushed to the code</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>AC-24</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>ddc0aa3, d89aeda (2026-04-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Peter asks how a unit will work once deployed on a client site; proposes a hotspot — at every boot the unit raises its own Wi-Fi hotspot and serves a web page from which the applications open</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Project Lead design review</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-05</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Deployment unit configuration; 0818cdc (2026-04-10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Client A reports live-transcript accuracy and speed problems — better speech model with fallback across models; chat moved from Ollama to TensorRT-LLM</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-06</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>d89aeda (04-08), b6a70d8 (06-26), 80375c6 (07-29)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Client C (law firm) likes conversation and live transcript; asks for a mode that listens, pulls up data while people speak and shows it on screen without replying — the Silent Assistant</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Client C</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-07</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>ec9b180 (05-11), f75121b (06-27), 7f2658a (08-16)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Group discussions: a diarisation model adopted after much trial and error in model selection — Boardroom</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-08</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>f540976 (05-14), cf463aa (05-19), e1a337b (05-27)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Client D (Gulf region) asks for a document studio — PPT and PDF created locally inside the application, with and without a template, with generated images</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Client D</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-09</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2d23f40 (06-20), 66356f9 (06-27)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Deliverable</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Review type</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Performed by</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Findings</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Record</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-01</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Platform for the next product generation</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Management / engineering review of the 2025 appliance against new hardware</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>EchoMind team</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>A single-PC appliance limits capacity and portability; a portable AI supercomputer is now available</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Decision recorded here; 4b90b36</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Requirements — Client A; Client B (Bahrain)</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Requirements review with the clients</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>EchoMind team with the clients</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>3 requirements: personal AI assistant; conversation assistance; DoD FMR financial knowledge base</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>95d3512, 18715c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-03</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Conversation assistance v1 (Kyutai Unmute stack)</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Client demonstration review</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Clients A and B</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>All five retrieval paths audited: 0 out-of-namespace hits across 359 checked; suite restored to 49/52</t>
+          <t>Not natural; too slow</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Commits ebd232f, 4e27109; eval/paper/results/REGRESSION_AND_FIXES.json</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Closed, effectiveness verified. Escalated to REG-04 NC-2026-001 and NC-2026-002</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4b90b36, bff6cf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03 → 04</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Conversation assistance v2 (NVIDIA PersonaPlex)</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Client demonstration review</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Clients A and B</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Fast, but cannot use the customer's large knowledge base in spoken conversation</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>ddc0aa3; QASC 2026 paper</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-05</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Field deployment of the unit</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Design review</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Peter (EchoMind Project Lead)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>No way to reach a deployed unit on a site without a network</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Deployment unit; 0818cdc</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Live transcription</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Client feedback review</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Accuracy and speed below need (e.g. 'DoD FMR' heard as 'DODFMA')</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>d89aeda, b6a70d8, 80375c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Conversation and live transcript demonstration</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Client review</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Client C (law firm)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Needs a listen-only assistant that pulls supporting data onto the screen while people speak</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>ec9b180, f75121b, 7f2658a</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Group discussions (Boardroom)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Design review and model trials</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>EchoMind team</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Speaker separation (diarisation) needed; model chosen by trial</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>f540976, cf463aa, e1a337b</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-09</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Document creation</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Client requirement review</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Client D (Gulf region)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>PPT and PDF made locally, with and without a template, with images</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2d23f40, 66356f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-01</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 → 08-07</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Retrieval pipeline</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Golden-question evaluation (52 questions) against the live stack</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>5 defects + 1 isolation regression</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>ebd232f, 4e27109 — REG-10 RF-2026-003</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-02</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Research paper experiment campaign (E1–E10)</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Measurements checked against the paper's own claims</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4 substantive (2 contradict published claims)</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>eval/paper/results/SUMMARY.json — RF-2026-002</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-03</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Voice change set (speculative reply, tool routing, GPU STT)</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Structured adversarial review, five lenses, each finding independently verified</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha (AI-assisted, independent verification)</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>40 raised; 22 confirmed; 18 refuted</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>ff29843 — RF-2026-001</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-04</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Golden evaluation re-run for audit evidence</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Measurement review</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Corpus absent (9/52)</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>NC-2026-008; eval_20260922-135322.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-05</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Repository health check</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Unit suites + type-check against HEAD</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>5 failing tests, 20 type errors</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>5ddf8a6, 736ea61 — NC-2026-010</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-06</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>October audit pack</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Every claim re-verified against the running system</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>6 statements wrong (incl. no login on the public site)</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>855bd80, 1d7f154 — NC-2026-009</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-07</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Release candidate (13 acceptance test cases)</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Executed acceptance tests, 4 runs</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>4 defects; re-tests found 2 more</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>e0ed4d0, 3feb5db, f1b8445 — NC-2026-012…016</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-08</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Public instance access logs</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Log review for the ungated period</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Ungated 68 days; 64 scanner probes; no data change outside engineering work</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>records/capa/2026-10-07_NC-2026-009_access_log_review.md</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Due</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Closure evidence</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Ticket</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-01</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Buy the first DGX Spark and port the 2025 code to it (ARM64)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>EchoMind team</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>4b90b36, c751d79 (2026-02-05) — 2025 code running on the DGX Spark</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>AC-21</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-02</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Personal AI assistant: financial-assistant behaviour, conversation memory, personas</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>95d3512, e59fd55 (2026-03-08); 518fb8e (2026-04-08); c6b834d (2026-06-27)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>AC-22</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-02</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>DoD FMR knowledge base: try BookRAG and PageIndex; adopt hierarchical section → chunk retrieval with table-of-contents routing and regulation-tuned query classification</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>31f1205, 045b1b1 (03-03); 18715c7, cfe3360 (03-05); 5057a30 (03-06). BookRAG 23ac2f9 (03-07) measured 43/52 vs 50/52 and was switched off (2decb99, 07-30); PageIndex evaluated, not adopted</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>AC-23</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-03</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Replace the Unmute stack with NVIDIA PersonaPlex</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Closed — superseded by AC-24</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Trial compared in the QASC 2026 paper; trial code not kept</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>AC-24</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-04</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Build our own dual-loop conversation architecture grounded in the customer's knowledge base</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ddc0aa3, d89aeda (04-08); fbbadd0 (05-28); 5ce8bbe, cbc57d1 (08-07) — 636 ms median first audio vs 866 ms single loop</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AC-25</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-05</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Hotspot: unit raises a Wi-Fi hotspot at every boot and serves a landing page that opens the applications</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Built on the deployment unit; offline preparation 0818cdc (2026-04-10)</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>AC-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-05</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Bring the hotspot configuration under version control and add it to the deployment guide</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Alexander Peter</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>AC-27</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-06</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Replace Whisper with Nemotron streaming speech recognition for live transcription</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>d89aeda, 172b94c, ddc0aa3</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AC-28</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-06</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Accurate final transcript with Parakeet-TDT and automatic fallback to the streaming model</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>b6a70d8, 3a6b1f9 — fixes 'DoD FMR' → 'DODFMA'</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>AC-29</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-06</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Move chat generation from Ollama to TensorRT-LLM for speed</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>06e788a (03-20) integration; 80375c6 (07-29) Qwen3-30B-A3B NVFP4 on TensorRT-LLM; Ollama kept for embeddings and rollback</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>AC-30</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-07</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Silent Assistant: runs with the live transcript; an assistant and an agent check the content continuously and surface data and pointers on screen without replying</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>ec9b180 (2026-05-11)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>AC-31</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-07</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Law rule pack, always-surface mode, namespace awareness; sentence-level checks with quoted proof</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>f75121b (06-27), 7f2658a (08-16)</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>AC-32</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-08</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Select a diarisation model by trial; build Boardroom (group discussion, speaker-separated transcript, report)</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>f540976 (05-14), cf463aa (05-19), e1a337b (05-27); VibeVoice-ASR adopted (REG-02 M-06)</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>AC-33</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-08</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Harden Boardroom: report salvage when the model output is truncated</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>b08cf25 (06-18), 724fb98 (09-04)</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>AC-34</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>CR-2026-09</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Evaluate image-generation and document models; build Document Studio with PDF and PPTX export, on-device images, with and without a template</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2d23f40 (06-20), 66356f9 (06-27); SDXL-Turbo on device (REG-02)</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>AC-01</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-01</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Enforce namespace predicate on the sparse transcript path; audit all paths</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>4e27109 — 0/359 out-of-namespace hits</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>AC-02</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-01</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Fix five retrieval defects found by the golden suite</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>ebd232f — suite restored to 49/52</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>AC-03</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-02</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Record contradicting findings verbatim; correct the claims in the next paper version</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Next version</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Open (recording done)</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>SUMMARY.json</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>#19, #27</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>AC-04</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-03</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>22 confirmed voice findings fixed before release (e.g. abort blocking the event loop; WebSocket close not aborting generation; hold phrase racing the answer; mid-word text split)</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>ff29843 — 12/12 spoken turns, barge-in verified, 0 CUDA errors</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>AC-05</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-04</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Make the evaluation abort when its corpus is missing</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>f3aca50 — aborts listing 15 documents</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>#48</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>AC-06</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-04</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Restore the evaluation corpus and re-measure</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>#47</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>AC-07</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-05</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Correct stale tests and type errors</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>5ddf8a6, 736ea61</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>AC-08</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-05</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Run the suites automatically on every push (CI)</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>CI runs 37561379960 (pass) / 37561804619 (fails on broken test)</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>#50</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>AC-09</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-06</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Restore application login on the public instance</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>Externally verified 401</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>#29</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>AC-10</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-06</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Correct the audit pack and registers against the running system</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>855bd80, 1d7f154</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>#40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>AC-11</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-07</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Logout revokes tokens; upload allow-list; small-talk routing; export key formats</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>e0ed4d0 + 14 regression tests; run 4 pass</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>#32–#35</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>AC-12</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-07</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Activity log identifies the caller before logout revokes the token</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>3feb5db; run 4 AC-101.8 pass</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>#32</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>AC-13</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-07</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Embedding service on CPU; healthcheck makes a real embedding</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>DC-2026-005; f3aca50</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>#59</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>AC-14</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-07</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Decide the GPU-sharing policy for the host</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>#60</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>AC-15</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-07</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Sign the v1.4.0 and v1.4.1 release records</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Anita Johan</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>#61</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>AC-16</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-08</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>External login check every 6 hours</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>run 37561803121</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>AC-17</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-08</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Record runtime-setting changes (SOP-06 §10.1, drift check)</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>f3aca50</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>AC-18</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-08</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Confirm the 2026-08-07 / 08-16 / 09-15 knowledge-base operations were internal; check Cloudflare analytics</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Kishan Haravu Pradeep</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>#53 follow-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>AC-19</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>RV-2026-08</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Record the real client address (CF-Connecting-IP) in the activity log; retain proxy logs</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Richard Watson Stephen Amudha</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
